--- a/output/yearly_surface_area_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_36_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497614814135</v>
+        <v>10.84497613700928</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907130050885</v>
+        <v>37.78907126171942</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.974916528046087</v>
+        <v>5.461462478725005</v>
       </c>
       <c r="C2" t="n">
-        <v>10.02069881724719</v>
+        <v>6.130032665317084</v>
       </c>
       <c r="D2" t="n">
-        <v>26.61419851442678</v>
+        <v>22.92184539875453</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.57266201121215</v>
+        <v>18.15251505152352</v>
       </c>
       <c r="C3" t="n">
-        <v>40.15838984221578</v>
+        <v>18.18196748265093</v>
       </c>
       <c r="D3" t="n">
-        <v>69.41447142877074</v>
+        <v>81.21017009529616</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.48563062289946</v>
+        <v>35.92705723691203</v>
       </c>
       <c r="C4" t="n">
-        <v>54.93074754801754</v>
+        <v>55.23705283174254</v>
       </c>
       <c r="D4" t="n">
-        <v>86.54400537246909</v>
+        <v>105.2158649595392</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.76078202199582</v>
+        <v>45.77398671050754</v>
       </c>
       <c r="C5" t="n">
-        <v>89.53539062730911</v>
+        <v>94.10051745205679</v>
       </c>
       <c r="D5" t="n">
-        <v>67.1024555852695</v>
+        <v>77.60715602071038</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.783722072092</v>
+        <v>42.42524529132167</v>
       </c>
       <c r="C6" t="n">
-        <v>118.0178550229176</v>
+        <v>99.42159000907451</v>
       </c>
       <c r="D6" t="n">
-        <v>47.97997380195012</v>
+        <v>51.92463607761381</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>29.2845522699781</v>
       </c>
       <c r="C7" t="n">
-        <v>104.0230414988793</v>
+        <v>73.60064363967912</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4352173326176</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>66.59194677906115</v>
+        <v>44.72842540548468</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>39.49374664644068</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>35.01894061048373</v>
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.702684856977935</v>
+        <v>7.707665811286438</v>
       </c>
       <c r="C21" t="n">
-        <v>95.32072510510196</v>
+        <v>95.38236441466967</v>
       </c>
       <c r="D21" t="n">
-        <v>8.665520464100178</v>
+        <v>8.671124037697242</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.874778262212914</v>
+        <v>7.578110529081129</v>
       </c>
       <c r="C2" t="n">
-        <v>10.88463679698439</v>
+        <v>4.974515617418588</v>
       </c>
       <c r="D2" t="n">
-        <v>27.32007511378024</v>
+        <v>20.73058452287565</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.97932654494859</v>
+        <v>18.2065111752571</v>
       </c>
       <c r="C3" t="n">
-        <v>39.32881303212722</v>
+        <v>21.12721059539136</v>
       </c>
       <c r="D3" t="n">
-        <v>73.40527584653401</v>
+        <v>81.21017009529616</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.44810322595982</v>
+        <v>35.03366682604742</v>
       </c>
       <c r="C4" t="n">
-        <v>78.00574558863457</v>
+        <v>50.10643932934871</v>
       </c>
       <c r="D4" t="n">
-        <v>98.40057239665781</v>
+        <v>118.2848903984727</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.17235529425349</v>
+        <v>50.09367660919352</v>
       </c>
       <c r="C5" t="n">
-        <v>94.37049807072466</v>
+        <v>97.95387719122553</v>
       </c>
       <c r="D5" t="n">
-        <v>81.26416621902975</v>
+        <v>95.59768270103318</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.59883470852411</v>
+        <v>51.64287448649497</v>
       </c>
       <c r="C6" t="n">
-        <v>130.0933517851534</v>
+        <v>122.7272987601895</v>
       </c>
       <c r="D6" t="n">
-        <v>56.39256987964104</v>
+        <v>62.26931163726245</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.47661496711198</v>
+        <v>39.46527596301753</v>
       </c>
       <c r="C7" t="n">
-        <v>135.1640786775881</v>
+        <v>107.7958979262998</v>
       </c>
       <c r="D7" t="n">
-        <v>43.77711188006952</v>
+        <v>45.39405034896402</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.02765316663493</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="C8" t="n">
-        <v>101.0561999366454</v>
+        <v>69.76299186377835</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>11.09374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>43.15468383557703</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>35.44600086183109</v>
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
         <v>37.13853390395258</v>
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.887527871114844</v>
+        <v>7.895242714042311</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5097442922717</v>
+        <v>104.6119659610606</v>
       </c>
       <c r="D21" t="n">
-        <v>9.859409838893555</v>
+        <v>9.869053392552889</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.372524348266047</v>
+        <v>8.669813976203582</v>
       </c>
       <c r="C2" t="n">
-        <v>16.3441357803009</v>
+        <v>15.48608828678919</v>
       </c>
       <c r="D2" t="n">
-        <v>25.63146906247573</v>
+        <v>22.54387253261951</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.98561794180156</v>
+        <v>21.43155238370787</v>
       </c>
       <c r="C3" t="n">
-        <v>40.85052197370978</v>
+        <v>20.09637550593221</v>
       </c>
       <c r="D3" t="n">
-        <v>76.67449570167589</v>
+        <v>78.7508920961579</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.92857876396402</v>
+        <v>34.63802250123597</v>
       </c>
       <c r="C4" t="n">
-        <v>86.33980184998573</v>
+        <v>51.28060958362789</v>
       </c>
       <c r="D4" t="n">
-        <v>109.6062406929309</v>
+        <v>127.8058796342583</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.7551125199486</v>
+        <v>50.95270585040947</v>
       </c>
       <c r="C5" t="n">
-        <v>115.5271610972434</v>
+        <v>94.2477796076938</v>
       </c>
       <c r="D5" t="n">
-        <v>93.56055621472105</v>
+        <v>112.9255296809894</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.31456984264904</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="C6" t="n">
-        <v>139.3109809803267</v>
+        <v>137.9424246806066</v>
       </c>
       <c r="D6" t="n">
-        <v>66.69699378341556</v>
+        <v>74.42531171124647</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.86074036137975</v>
+        <v>49.22679338634357</v>
       </c>
       <c r="C7" t="n">
-        <v>157.8012172421111</v>
+        <v>138.1584091755409</v>
       </c>
       <c r="D7" t="n">
-        <v>48.38838084691679</v>
+        <v>51.86180422454201</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.03733177495716</v>
+        <v>32.12769362147687</v>
       </c>
       <c r="C8" t="n">
-        <v>135.0197617650638</v>
+        <v>102.808619588726</v>
       </c>
       <c r="D8" t="n">
         <v>41.30703465618455</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.64374875654542</v>
+        <v>16.30781111524376</v>
       </c>
       <c r="C9" t="n">
-        <v>88.86092995449152</v>
+        <v>62.12499472473814</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>52.52841091572559</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.056400376798914</v>
+        <v>8.068789219433093</v>
       </c>
       <c r="C21" t="n">
-        <v>112.7896052751848</v>
+        <v>112.9630490720633</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0775505180985</v>
+        <v>11.0945851767205</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.871833019100173</v>
+        <v>7.822565707438585</v>
       </c>
       <c r="C2" t="n">
-        <v>10.98281156740907</v>
+        <v>10.28184370657685</v>
       </c>
       <c r="D2" t="n">
-        <v>21.09383117344697</v>
+        <v>18.45882033524853</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.29901644363455</v>
+        <v>25.2260072606218</v>
       </c>
       <c r="C3" t="n">
-        <v>63.06256378229386</v>
+        <v>37.394770054761</v>
       </c>
       <c r="D3" t="n">
-        <v>83.20802667343843</v>
+        <v>88.10694771763001</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.53521672973053</v>
+        <v>24.47889725768997</v>
       </c>
       <c r="C4" t="n">
-        <v>105.7391364859027</v>
+        <v>76.5763209312512</v>
       </c>
       <c r="D4" t="n">
-        <v>105.7518992060579</v>
+        <v>124.6790131962322</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.34796496012666</v>
+        <v>33.011266555299</v>
       </c>
       <c r="C5" t="n">
-        <v>83.22766162752336</v>
+        <v>82.41771977151974</v>
       </c>
       <c r="D5" t="n">
-        <v>65.89981464756715</v>
+        <v>75.88909753827845</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.96231803880691</v>
+        <v>30.5510068084565</v>
       </c>
       <c r="C6" t="n">
-        <v>103.9297754669759</v>
+        <v>90.96874227550947</v>
       </c>
       <c r="D6" t="n">
-        <v>31.83905979642831</v>
+        <v>34.13340418125311</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="C7" t="n">
-        <v>94.92027678510286</v>
+        <v>72.2831382205799</v>
       </c>
       <c r="D7" t="n">
         <v>29.04500583014188</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>65.42366701100744</v>
+        <v>45.72980806381643</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>18.41660518396592</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.523492510541802</v>
+        <v>4.613232462255762</v>
       </c>
       <c r="C2" t="n">
-        <v>5.098215828153687</v>
+        <v>4.782093067386213</v>
       </c>
       <c r="D2" t="n">
-        <v>15.49492401612741</v>
+        <v>12.87758463660541</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.4217349066654</v>
+        <v>26.89497835784137</v>
       </c>
       <c r="C3" t="n">
-        <v>53.71632563786423</v>
+        <v>39.74605580643212</v>
       </c>
       <c r="D3" t="n">
-        <v>81.44088080579417</v>
+        <v>84.33703653332225</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.63503620039422</v>
+        <v>35.54417563225577</v>
       </c>
       <c r="C4" t="n">
-        <v>134.9785283614855</v>
+        <v>87.83304010814514</v>
       </c>
       <c r="D4" t="n">
-        <v>121.5521467582061</v>
+        <v>138.1181575196668</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.92505268377453</v>
+        <v>36.34920874973816</v>
       </c>
       <c r="C5" t="n">
-        <v>135.063940411755</v>
+        <v>111.2565585837698</v>
       </c>
       <c r="D5" t="n">
-        <v>82.29500130848889</v>
+        <v>97.78207134298233</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.19503330244241</v>
+        <v>37.0315234041897</v>
       </c>
       <c r="C6" t="n">
-        <v>120.4732060312389</v>
+        <v>112.5838814799115</v>
       </c>
       <c r="D6" t="n">
-        <v>39.68813269188156</v>
+        <v>43.39128503230054</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="C7" t="n">
-        <v>119.5935600882337</v>
+        <v>96.53721525399735</v>
       </c>
       <c r="D7" t="n">
-        <v>31.68001666834032</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>85.61821728736433</v>
+        <v>61.66848204226339</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>46.26093357181394</v>
+        <v>37.71874679716245</v>
       </c>
       <c r="D9" t="n">
         <v>28.73281006019139</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.70599977254047</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.545090960035232</v>
+        <v>5.271003424101125</v>
       </c>
       <c r="C2" t="n">
-        <v>7.273768740764618</v>
+        <v>5.458517235612265</v>
       </c>
       <c r="D2" t="n">
-        <v>13.70519795128547</v>
+        <v>18.51085296357361</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64553232550467</v>
+        <v>21.1762979806037</v>
       </c>
       <c r="C3" t="n">
-        <v>35.86815237465722</v>
+        <v>28.25960766674444</v>
       </c>
       <c r="D3" t="n">
-        <v>76.04617717095793</v>
+        <v>75.65838682778045</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.32720938961722</v>
+        <v>43.77613013236527</v>
       </c>
       <c r="C4" t="n">
-        <v>134.4552568351219</v>
+        <v>93.89533218186919</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5663742521511</v>
+        <v>147.9326893190221</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.20823799095412</v>
+        <v>44.44862730977434</v>
       </c>
       <c r="C5" t="n">
-        <v>190.8026663203676</v>
+        <v>138.2300767579509</v>
       </c>
       <c r="D5" t="n">
-        <v>103.0344215607028</v>
+        <v>122.1785017935156</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.14598697495907</v>
+        <v>42.94851681768522</v>
       </c>
       <c r="C6" t="n">
-        <v>166.0380804807419</v>
+        <v>143.6179081588574</v>
       </c>
       <c r="D6" t="n">
-        <v>52.85042416271855</v>
+        <v>60.73974871404592</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>30.24273802932299</v>
       </c>
       <c r="C7" t="n">
-        <v>146.4227613498905</v>
+        <v>129.4149641215188</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>118.9141906768949</v>
+        <v>92.87824156026949</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>71.77655640518853</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
         <v>29.50937249425062</v>
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>42.42131830050468</v>
+        <v>37.43894870145212</v>
       </c>
       <c r="D10" t="n">
         <v>30.7483380970101</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.100940087088174</v>
+        <v>3.088578277560466</v>
       </c>
       <c r="C2" t="n">
-        <v>3.388011327355743</v>
+        <v>2.457314503729767</v>
       </c>
       <c r="D2" t="n">
-        <v>9.562222639363933</v>
+        <v>12.75584792127881</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.30682936753952</v>
+        <v>21.65735435568464</v>
       </c>
       <c r="C3" t="n">
-        <v>34.94530953266521</v>
+        <v>26.96860943565988</v>
       </c>
       <c r="D3" t="n">
-        <v>73.55744674069227</v>
+        <v>75.73201790559895</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.82419471214436</v>
+        <v>48.38347210839555</v>
       </c>
       <c r="C4" t="n">
-        <v>131.1114241544573</v>
+        <v>93.89533218186919</v>
       </c>
       <c r="D4" t="n">
-        <v>141.0408204352095</v>
+        <v>155.207439807491</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.90175278077987</v>
+        <v>46.55938487390499</v>
       </c>
       <c r="C5" t="n">
-        <v>234.5640702371692</v>
+        <v>168.4433623561465</v>
       </c>
       <c r="D5" t="n">
-        <v>108.7285582453343</v>
+        <v>131.8241729877405</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.3497485290859</v>
+        <v>36.6290068454485</v>
       </c>
       <c r="C6" t="n">
-        <v>198.8029283622749</v>
+        <v>176.7450209432575</v>
       </c>
       <c r="D6" t="n">
-        <v>51.84413276586557</v>
+        <v>59.29068910257763</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.024805734513427</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>155.2260930138717</v>
+        <v>131.2714490302495</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>88.95615948180348</v>
+        <v>71.01472018669303</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
+        <v>28.51093507903161</v>
+      </c>
+      <c r="D9" t="n">
         <v>32.39374724932775</v>
-      </c>
-      <c r="D9" t="n">
-        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.90016483380309</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.273727683035613</v>
+        <v>3.689407872559513</v>
       </c>
       <c r="C2" t="n">
-        <v>4.338343105066655</v>
+        <v>9.196030745679874</v>
       </c>
       <c r="D2" t="n">
-        <v>9.859692193750716</v>
+        <v>12.01168316145973</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.91841712955628</v>
+        <v>16.25774198232718</v>
       </c>
       <c r="C3" t="n">
-        <v>23.88101290580366</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="D3" t="n">
-        <v>65.81636609270616</v>
+        <v>69.01686360855078</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.5824637927214</v>
+        <v>45.1545039091278</v>
       </c>
       <c r="C4" t="n">
-        <v>110.7038346262788</v>
+        <v>81.1964256274367</v>
       </c>
       <c r="D4" t="n">
-        <v>144.4612294368054</v>
+        <v>157.28776319279</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.0502587260284</v>
+        <v>58.14400778401735</v>
       </c>
       <c r="C5" t="n">
-        <v>239.6937019918588</v>
+        <v>172.1249162470721</v>
       </c>
       <c r="D5" t="n">
-        <v>128.8052987971815</v>
+        <v>153.3980787885641</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.7220929509027</v>
+        <v>47.61770889908305</v>
       </c>
       <c r="C6" t="n">
-        <v>275.6835910818426</v>
+        <v>219.774041072691</v>
       </c>
       <c r="D6" t="n">
-        <v>68.14605339488386</v>
+        <v>81.67060976858792</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>20.78065365579224</v>
       </c>
       <c r="C7" t="n">
-        <v>211.75905281522</v>
+        <v>187.984068661475</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>42.51949307092936</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>137.6901155206152</v>
+        <v>113.9907259400971</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>59.90624491314035</v>
+        <v>51.25312064790897</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.713149743910684</v>
+        <v>2.674280746368311</v>
       </c>
       <c r="C2" t="n">
-        <v>2.479894700927443</v>
+        <v>4.464006811210247</v>
       </c>
       <c r="D2" t="n">
-        <v>7.258060777496669</v>
+        <v>9.280461048245099</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.28871594050657</v>
+        <v>14.86856898081794</v>
       </c>
       <c r="C3" t="n">
-        <v>20.930861054542</v>
+        <v>26.48264432205771</v>
       </c>
       <c r="D3" t="n">
-        <v>60.88308387886595</v>
+        <v>64.18666490365646</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.56220694383071</v>
+        <v>40.39400929123502</v>
       </c>
       <c r="C4" t="n">
-        <v>91.98092415858791</v>
+        <v>67.08085713577607</v>
       </c>
       <c r="D4" t="n">
-        <v>144.7802974406856</v>
+        <v>156.981457909065</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.07542431344032</v>
+        <v>63.93631923907354</v>
       </c>
       <c r="C5" t="n">
-        <v>234.392264388926</v>
+        <v>169.1551294417254</v>
       </c>
       <c r="D5" t="n">
-        <v>141.837999571058</v>
+        <v>168.8360614378452</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.16235789076178</v>
+        <v>56.35231822376692</v>
       </c>
       <c r="C6" t="n">
-        <v>322.2950085840727</v>
+        <v>248.795484957931</v>
       </c>
       <c r="D6" t="n">
-        <v>81.67060976858792</v>
+        <v>96.96623900075323</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.4507453694363</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>272.8433949734565</v>
+        <v>236.1927896785146</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>48.44826745687584</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>175.0750680983337</v>
+        <v>149.7067074205961</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>68.22655670663207</v>
+        <v>62.45780719647781</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.268818944514379</v>
+        <v>5.117850782238622</v>
       </c>
       <c r="C2" t="n">
-        <v>15.52732169036755</v>
+        <v>5.312236827679491</v>
       </c>
       <c r="D2" t="n">
-        <v>16.91649469187679</v>
+        <v>10.60876569209103</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.163232160812228</v>
+        <v>12.04113559258713</v>
       </c>
       <c r="C3" t="n">
-        <v>15.81595551541612</v>
+        <v>22.19240685449915</v>
       </c>
       <c r="D3" t="n">
-        <v>54.03539364174444</v>
+        <v>58.31581363226054</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.98489823600458</v>
+        <v>34.5486834601495</v>
       </c>
       <c r="C4" t="n">
-        <v>73.67918345601888</v>
+        <v>65.8045851202552</v>
       </c>
       <c r="D4" t="n">
-        <v>142.3170924507304</v>
+        <v>152.1188615299305</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.62734644967627</v>
+        <v>63.32272692391928</v>
       </c>
       <c r="C5" t="n">
-        <v>206.3142800474673</v>
+        <v>150.2810298275805</v>
       </c>
       <c r="D5" t="n">
-        <v>155.8769917417874</v>
+        <v>182.8505099159684</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.017722183068</v>
+        <v>67.94479511551327</v>
       </c>
       <c r="C6" t="n">
-        <v>343.4271279179853</v>
+        <v>257.892359185482</v>
       </c>
       <c r="D6" t="n">
-        <v>99.46184166494862</v>
+        <v>119.8694311931271</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.086820070797</v>
+        <v>36.29128563518759</v>
       </c>
       <c r="C7" t="n">
-        <v>352.3129263891231</v>
+        <v>287.2760679735889</v>
       </c>
       <c r="D7" t="n">
-        <v>53.41885608347744</v>
+        <v>60.12615639889166</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>245.3387512912779</v>
+        <v>216.1317570899353</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>122.0312396378785</v>
+        <v>107.8312408436526</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>49.11192890494669</v>
+        <v>47.40368789955724</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
         <v>16.91060420565131</v>
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.489532251520663</v>
+        <v>4.691772278595507</v>
       </c>
       <c r="C2" t="n">
-        <v>6.714172549343935</v>
+        <v>3.16711809390021</v>
       </c>
       <c r="D2" t="n">
-        <v>7.091163667774712</v>
+        <v>9.152833846693014</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.64050041379642</v>
+        <v>3.618722037853743</v>
       </c>
       <c r="C2" t="n">
-        <v>8.943721585688444</v>
+        <v>2.974695543867836</v>
       </c>
       <c r="D2" t="n">
-        <v>12.58502382073986</v>
+        <v>7.807839491874883</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.09374905798896</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="C3" t="n">
-        <v>31.05267988532661</v>
+        <v>25.11801501315465</v>
       </c>
       <c r="D3" t="n">
-        <v>60.28421777927539</v>
+        <v>63.30800070835556</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.088464771036</v>
+        <v>47.74533610063513</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6617994014455</v>
+        <v>93.06575537178064</v>
       </c>
       <c r="D4" t="n">
-        <v>146.5032646616388</v>
+        <v>157.7089329579119</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.34229545807943</v>
+        <v>40.61981126321179</v>
       </c>
       <c r="C5" t="n">
-        <v>298.9176322505476</v>
+        <v>221.2859325372311</v>
       </c>
       <c r="D5" t="n">
-        <v>141.9361743414826</v>
+        <v>169.2042168269378</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.42896699349363</v>
+        <v>22.50067563363265</v>
       </c>
       <c r="C6" t="n">
-        <v>295.9704256423987</v>
+        <v>242.2747167063237</v>
       </c>
       <c r="D6" t="n">
-        <v>79.33601372788901</v>
+        <v>93.18258334858602</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>172.5333232920387</v>
+        <v>151.9922160760827</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>89.95754214013523</v>
+        <v>79.44302422765189</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
         <v>13.66887328622834</v>
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.943500601510189</v>
+        <v>6.93801102591221</v>
       </c>
       <c r="C2" t="n">
-        <v>2.830378631343554</v>
+        <v>3.323215978875453</v>
       </c>
       <c r="D2" t="n">
-        <v>21.39326422324224</v>
+        <v>23.18888077430966</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.542587685278997</v>
+        <v>9.969647936626359</v>
       </c>
       <c r="C3" t="n">
-        <v>17.18549356284042</v>
+        <v>8.10432729855742</v>
       </c>
       <c r="D3" t="n">
-        <v>9.090983741325465</v>
+        <v>11.19192382841364</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39886202116786</v>
+        <v>13.3990828190242</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14698352258468</v>
+        <v>70.14813946430317</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576336708372689</v>
+        <v>1.576362684591082</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.910301106015046</v>
+        <v>5.202281084803848</v>
       </c>
       <c r="C2" t="n">
-        <v>8.458738219790517</v>
+        <v>4.636794407157685</v>
       </c>
       <c r="D2" t="n">
-        <v>21.83995942867454</v>
+        <v>28.31556728588651</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.10557108816893</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C3" t="n">
-        <v>13.33704256219292</v>
+        <v>11.27537238327462</v>
       </c>
       <c r="D3" t="n">
-        <v>24.86276061005047</v>
+        <v>27.96508335547039</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.20566829627309</v>
+        <v>11.69065166217102</v>
       </c>
       <c r="C4" t="n">
-        <v>26.71237328485147</v>
+        <v>12.89034735676062</v>
       </c>
       <c r="D4" t="n">
-        <v>19.83326712119406</v>
+        <v>20.930861054542</v>
       </c>
     </row>
     <row r="5">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44263378003365</v>
+        <v>15.44350206053287</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15364108860879</v>
+        <v>86.15848517981495</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251080795796558</v>
+        <v>3.25126359169113</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.154756284372501</v>
+        <v>5.223879534297278</v>
       </c>
       <c r="C2" t="n">
-        <v>7.422994391810134</v>
+        <v>7.565347808925921</v>
       </c>
       <c r="D2" t="n">
-        <v>19.64771680509142</v>
+        <v>25.24367871929824</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.65749322440488</v>
+        <v>18.15251505152352</v>
       </c>
       <c r="C3" t="n">
-        <v>25.21128104505809</v>
+        <v>15.37907778702628</v>
       </c>
       <c r="D3" t="n">
-        <v>36.56519324467245</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.4368620328566</v>
+        <v>25.05321966467436</v>
       </c>
       <c r="C4" t="n">
-        <v>30.6560538128109</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D4" t="n">
-        <v>27.82272993835461</v>
+        <v>30.23488404768902</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.33289458719768</v>
+        <v>10.70104997629023</v>
       </c>
       <c r="C5" t="n">
-        <v>30.38509144643879</v>
+        <v>15.83068173097982</v>
       </c>
       <c r="D5" t="n">
-        <v>29.57514959043517</v>
+        <v>29.96784867213389</v>
       </c>
     </row>
     <row r="6">
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.52854978444583</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73798533578417</v>
+        <v>16.73988753003033</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1017105482835</v>
+        <v>102.113313933185</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021395600735253</v>
+        <v>5.0219662590091</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.017712516405448</v>
+        <v>5.630323083855457</v>
       </c>
       <c r="C2" t="n">
-        <v>4.523893421169302</v>
+        <v>6.924266558052754</v>
       </c>
       <c r="D2" t="n">
-        <v>19.84406634594078</v>
+        <v>20.56466916085794</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.42678251390688</v>
+        <v>18.01507037292897</v>
       </c>
       <c r="C3" t="n">
-        <v>27.27295122397639</v>
+        <v>23.59630607157209</v>
       </c>
       <c r="D3" t="n">
-        <v>43.36379609658162</v>
+        <v>53.50034114292993</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.76793199336603</v>
+        <v>30.41356212986194</v>
       </c>
       <c r="C4" t="n">
-        <v>48.47281114948201</v>
+        <v>31.34524070119216</v>
       </c>
       <c r="D4" t="n">
-        <v>38.96458463385165</v>
+        <v>44.42702886028091</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.86843011209771</v>
+        <v>24.39643045053324</v>
       </c>
       <c r="C5" t="n">
-        <v>44.8167826988669</v>
+        <v>29.37880004958581</v>
       </c>
       <c r="D5" t="n">
-        <v>33.03581024790518</v>
+        <v>34.18936380039518</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.982410656781569</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>31.19503330244241</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>38.27932473628739</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
         <v>39.46527596301753</v>
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.77765165941727</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06744446299536</v>
+        <v>18.07137851900765</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8685662585888</v>
+        <v>117.8942312906689</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882835985902996</v>
+        <v>6.884334673907674</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.828636120113313</v>
+        <v>5.98964274360979</v>
       </c>
       <c r="C2" t="n">
-        <v>4.876340846993907</v>
+        <v>6.073091298470769</v>
       </c>
       <c r="D2" t="n">
-        <v>24.9452274172072</v>
+        <v>31.29517156827557</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.32369900496096</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C3" t="n">
-        <v>20.33690369347268</v>
+        <v>24.01354884587698</v>
       </c>
       <c r="D3" t="n">
-        <v>45.91143138910209</v>
+        <v>53.84395283941632</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.76945352041802</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C4" t="n">
-        <v>50.06815116888308</v>
+        <v>39.51338160052563</v>
       </c>
       <c r="D4" t="n">
-        <v>44.37597797966007</v>
+        <v>52.28886447588937</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.57957530287089</v>
+        <v>21.50027472300515</v>
       </c>
       <c r="C5" t="n">
-        <v>51.49266708774522</v>
+        <v>33.23215978875454</v>
       </c>
       <c r="D5" t="n">
-        <v>32.15223731408305</v>
+        <v>34.45934441906305</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.94845039776043</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>35.17994723398021</v>
+        <v>22.86294053649972</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>31.15478164656829</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>21.4992929753009</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="D7" t="n">
         <v>31.14103717870882</v>
@@ -5846,7 +5846,7 @@
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063524439512785</v>
+        <v>7.066271714541922</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22054162043237</v>
+        <v>66.24629732383052</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297643329634589</v>
+        <v>5.299703785906441</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.457134577280519</v>
+        <v>5.43888228152733</v>
       </c>
       <c r="C2" t="n">
-        <v>6.896777622333842</v>
+        <v>5.155157195000002</v>
       </c>
       <c r="D2" t="n">
-        <v>21.92733497435251</v>
+        <v>31.6731444344106</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.08870145074748</v>
+        <v>19.64968030049991</v>
       </c>
       <c r="C3" t="n">
-        <v>19.50732688338412</v>
+        <v>23.84174299763379</v>
       </c>
       <c r="D3" t="n">
-        <v>56.32777453116074</v>
+        <v>67.85349257901831</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.90006702281185</v>
+        <v>29.54569715930776</v>
       </c>
       <c r="C4" t="n">
-        <v>50.74457533710914</v>
+        <v>52.77384784178729</v>
       </c>
       <c r="D4" t="n">
-        <v>58.86166535582176</v>
+        <v>69.21223140169589</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.42726553999239</v>
+        <v>30.48326621686347</v>
       </c>
       <c r="C5" t="n">
-        <v>77.06719478337463</v>
+        <v>57.97220193577417</v>
       </c>
       <c r="D5" t="n">
-        <v>41.89608327873264</v>
+        <v>46.73119072214818</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.32079481957723</v>
+        <v>21.89690079552086</v>
       </c>
       <c r="C6" t="n">
-        <v>63.11459641061895</v>
+        <v>40.57366912111219</v>
       </c>
       <c r="D6" t="n">
-        <v>34.29441080474959</v>
+        <v>35.26045054572845</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="C7" t="n">
-        <v>38.98618308334508</v>
+        <v>26.29022177202533</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>24.53387512912779</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6199,7 +6199,7 @@
         <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.288910355086936</v>
+        <v>7.292359739057018</v>
       </c>
       <c r="C21" t="n">
-        <v>76.53355872841284</v>
+        <v>76.56977726009869</v>
       </c>
       <c r="D21" t="n">
-        <v>6.37779656070107</v>
+        <v>6.38081477167489</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.224059460746525</v>
+        <v>5.053055433758333</v>
       </c>
       <c r="C2" t="n">
-        <v>13.53339210304228</v>
+        <v>4.059526757060561</v>
       </c>
       <c r="D2" t="n">
-        <v>29.1333631235241</v>
+        <v>27.61950816357552</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.61607989437726</v>
+        <v>19.24716374175872</v>
       </c>
       <c r="C3" t="n">
-        <v>24.04300127700439</v>
+        <v>21.52481841561132</v>
       </c>
       <c r="D3" t="n">
-        <v>60.79963532400497</v>
+        <v>77.44516764950964</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.06446085777758</v>
+        <v>34.8422260237193</v>
       </c>
       <c r="C4" t="n">
-        <v>49.67250684407162</v>
+        <v>56.9727827728509</v>
       </c>
       <c r="D4" t="n">
-        <v>73.32182729167303</v>
+        <v>87.0162260182118</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.0295188510522</v>
+        <v>38.14089830998859</v>
       </c>
       <c r="C5" t="n">
-        <v>86.88467182584273</v>
+        <v>80.99418560036187</v>
       </c>
       <c r="D5" t="n">
-        <v>54.29064804484862</v>
+        <v>61.87464906015524</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.89439752076462</v>
+        <v>32.80509953740717</v>
       </c>
       <c r="C6" t="n">
-        <v>95.75868932452966</v>
+        <v>68.99133816824036</v>
       </c>
       <c r="D6" t="n">
-        <v>40.09064925062275</v>
+        <v>42.30449032369931</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>68.57016840311847</v>
+        <v>44.6155244194963</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>39.97185777840888</v>
+        <v>28.78975142703771</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>25.18281036163492</v>
       </c>
       <c r="D9" t="n">
         <v>32.50468473990763</v>
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.502855886799171</v>
+        <v>7.506489184641604</v>
       </c>
       <c r="C21" t="n">
-        <v>86.28284269819046</v>
+        <v>86.32462562337845</v>
       </c>
       <c r="D21" t="n">
-        <v>7.502855886799171</v>
+        <v>7.506489184641604</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_36_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497613700928</v>
+        <v>10.84497647746983</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907126171942</v>
+        <v>37.78907244804643</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.461462478725005</v>
+        <v>5.964117303299373</v>
       </c>
       <c r="C2" t="n">
-        <v>6.130032665317084</v>
+        <v>6.640541471525426</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92184539875453</v>
+        <v>16.47176298185299</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.15251505152352</v>
+        <v>17.37202562664731</v>
       </c>
       <c r="C3" t="n">
-        <v>18.18196748265093</v>
+        <v>31.43065275146164</v>
       </c>
       <c r="D3" t="n">
-        <v>81.21017009529616</v>
+        <v>52.1111681414207</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.92705723691203</v>
+        <v>34.34447993766616</v>
       </c>
       <c r="C4" t="n">
-        <v>55.23705283174254</v>
+        <v>65.12816095202915</v>
       </c>
       <c r="D4" t="n">
-        <v>105.2158649595392</v>
+        <v>70.19496085364693</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.77398671050754</v>
+        <v>40.86524818927349</v>
       </c>
       <c r="C5" t="n">
-        <v>94.10051745205679</v>
+        <v>122.2521328713341</v>
       </c>
       <c r="D5" t="n">
-        <v>77.60715602071038</v>
+        <v>56.47503668679778</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.42524529132167</v>
+        <v>37.07177506006381</v>
       </c>
       <c r="C6" t="n">
-        <v>99.42159000907451</v>
+        <v>139.2304776685784</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>43.23027840880406</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.2845522699781</v>
+        <v>25.87101550231194</v>
       </c>
       <c r="C7" t="n">
-        <v>73.60064363967912</v>
+        <v>125.5223344741802</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>44.72842540548468</v>
+        <v>94.54721265748907</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>30.95155987178918</v>
+        <v>53.13905798776709</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.707665811286438</v>
+        <v>7.6814867953624</v>
       </c>
       <c r="C21" t="n">
-        <v>95.38236441466967</v>
+        <v>93.13802739376909</v>
       </c>
       <c r="D21" t="n">
-        <v>8.671124037697242</v>
+        <v>7.6814867953624</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.578110529081129</v>
+        <v>7.032258805519903</v>
       </c>
       <c r="C2" t="n">
-        <v>4.974515617418588</v>
+        <v>12.03328161095315</v>
       </c>
       <c r="D2" t="n">
-        <v>20.73058452287565</v>
+        <v>15.30348321379928</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2065111752571</v>
+        <v>18.75138115111408</v>
       </c>
       <c r="C3" t="n">
-        <v>21.12721059539136</v>
+        <v>28.36759991421159</v>
       </c>
       <c r="D3" t="n">
-        <v>81.21017009529616</v>
+        <v>52.71985171805372</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.03366682604742</v>
+        <v>33.32346232524949</v>
       </c>
       <c r="C4" t="n">
-        <v>50.10643932934871</v>
+        <v>71.72648727227197</v>
       </c>
       <c r="D4" t="n">
-        <v>118.2848903984727</v>
+        <v>78.70769519717103</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.09367660919352</v>
+        <v>45.52854978444584</v>
       </c>
       <c r="C5" t="n">
-        <v>97.95387719122553</v>
+        <v>119.8959383811417</v>
       </c>
       <c r="D5" t="n">
-        <v>95.59768270103318</v>
+        <v>66.26797003665972</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.64287448649497</v>
+        <v>45.36361617013237</v>
       </c>
       <c r="C6" t="n">
-        <v>122.7272987601895</v>
+        <v>165.4745572985042</v>
       </c>
       <c r="D6" t="n">
-        <v>62.26931163726245</v>
+        <v>50.2340665309008</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.61446055633404</v>
       </c>
       <c r="C7" t="n">
-        <v>107.7958979262998</v>
+        <v>160.1966816404733</v>
       </c>
       <c r="D7" t="n">
-        <v>45.39405034896402</v>
+        <v>41.3816474817073</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.19869825135213</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C8" t="n">
-        <v>69.76299186377835</v>
+        <v>129.0949143699343</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>10.42812411450962</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>82.42655550085793</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.895242714042311</v>
+        <v>7.861393332066825</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6119659610606</v>
+        <v>101.2154391503604</v>
       </c>
       <c r="D21" t="n">
-        <v>9.869053392552889</v>
+        <v>8.844067498575178</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.669813976203582</v>
+        <v>8.275151399096364</v>
       </c>
       <c r="C2" t="n">
-        <v>15.48608828678919</v>
+        <v>13.44798005277281</v>
       </c>
       <c r="D2" t="n">
-        <v>22.54387253261951</v>
+        <v>28.84472929847554</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.43155238370787</v>
+        <v>20.59215809657685</v>
       </c>
       <c r="C3" t="n">
-        <v>20.09637550593221</v>
+        <v>37.11497195905067</v>
       </c>
       <c r="D3" t="n">
-        <v>78.7508920961579</v>
+        <v>52.81311774995717</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.63802250123597</v>
+        <v>33.66805576944012</v>
       </c>
       <c r="C4" t="n">
-        <v>51.28060958362789</v>
+        <v>70.41192709628548</v>
       </c>
       <c r="D4" t="n">
-        <v>127.8058796342583</v>
+        <v>83.95317318096176</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.95270585040947</v>
+        <v>47.5411325781518</v>
       </c>
       <c r="C5" t="n">
-        <v>94.2477796076938</v>
+        <v>123.8474728907351</v>
       </c>
       <c r="D5" t="n">
-        <v>112.9255296809894</v>
+        <v>75.86455384567229</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.6064109527176</v>
+        <v>51.80388110999145</v>
       </c>
       <c r="C6" t="n">
-        <v>137.9424246806066</v>
+        <v>176.8255242550058</v>
       </c>
       <c r="D6" t="n">
-        <v>74.42531171124647</v>
+        <v>57.9623844587317</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.22679338634357</v>
+        <v>42.57937968088841</v>
       </c>
       <c r="C7" t="n">
-        <v>138.1584091755409</v>
+        <v>193.0744305079947</v>
       </c>
       <c r="D7" t="n">
-        <v>51.86180422454201</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.12769362147687</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="C8" t="n">
-        <v>102.808619588726</v>
+        <v>164.6439987407113</v>
       </c>
       <c r="D8" t="n">
-        <v>41.30703465618455</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.30781111524376</v>
+        <v>14.64374875654542</v>
       </c>
       <c r="C9" t="n">
-        <v>62.12499472473814</v>
+        <v>116.3734276183041</v>
       </c>
       <c r="D9" t="n">
-        <v>37.71874679716245</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>67.90257996423065</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>42.11403126907541</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.068789219433093</v>
+        <v>8.025718301366755</v>
       </c>
       <c r="C21" t="n">
-        <v>112.9630490720633</v>
+        <v>109.350411856122</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0945851767205</v>
+        <v>10.03214787670844</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.822565707438585</v>
+        <v>7.539822368615503</v>
       </c>
       <c r="C2" t="n">
-        <v>10.28184370657685</v>
+        <v>9.143998117354792</v>
       </c>
       <c r="D2" t="n">
-        <v>18.45882033524853</v>
+        <v>23.58256160371263</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.2260072606218</v>
+        <v>24.01354884587698</v>
       </c>
       <c r="C3" t="n">
-        <v>37.394770054761</v>
+        <v>54.87478792887547</v>
       </c>
       <c r="D3" t="n">
-        <v>88.10694771763001</v>
+        <v>58.0801941832413</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.47889725768997</v>
+        <v>22.83250635766807</v>
       </c>
       <c r="C4" t="n">
-        <v>76.5763209312512</v>
+        <v>100.3532685804047</v>
       </c>
       <c r="D4" t="n">
-        <v>124.6790131962322</v>
+        <v>82.06429059799088</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.011266555299</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C5" t="n">
-        <v>82.41771977151974</v>
+        <v>105.660596669563</v>
       </c>
       <c r="D5" t="n">
-        <v>75.88909753827845</v>
+        <v>55.02695882303374</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.5510068084565</v>
+        <v>26.40508625342222</v>
       </c>
       <c r="C6" t="n">
-        <v>90.96874227550947</v>
+        <v>127.1549809063427</v>
       </c>
       <c r="D6" t="n">
-        <v>34.13340418125311</v>
+        <v>29.66547037922588</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="C7" t="n">
-        <v>72.2831382205799</v>
+        <v>115.7608170508541</v>
       </c>
       <c r="D7" t="n">
-        <v>29.04500583014188</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>45.72980806381643</v>
+        <v>85.78511439708629</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>31.50624732468863</v>
+        <v>51.80780810080841</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.93362637120549</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.613232462255762</v>
+        <v>4.524875168873549</v>
       </c>
       <c r="C2" t="n">
-        <v>4.782093067386213</v>
+        <v>4.35503281603885</v>
       </c>
       <c r="D2" t="n">
-        <v>12.87758463660541</v>
+        <v>16.68774747678728</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.89497835784137</v>
+        <v>25.56471021858694</v>
       </c>
       <c r="C3" t="n">
-        <v>39.74605580643212</v>
+        <v>46.04396732917541</v>
       </c>
       <c r="D3" t="n">
-        <v>84.33703653332225</v>
+        <v>62.87112297996573</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.54417563225577</v>
+        <v>32.67256359733385</v>
       </c>
       <c r="C4" t="n">
-        <v>87.83304010814514</v>
+        <v>120.6459936271863</v>
       </c>
       <c r="D4" t="n">
-        <v>138.1181575196668</v>
+        <v>91.72566975548375</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.34920874973816</v>
+        <v>32.79037332184348</v>
       </c>
       <c r="C5" t="n">
-        <v>111.2565585837698</v>
+        <v>144.5623494503429</v>
       </c>
       <c r="D5" t="n">
-        <v>97.78207134298233</v>
+        <v>67.22517404830035</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.0315234041897</v>
+        <v>31.35603992593888</v>
       </c>
       <c r="C6" t="n">
-        <v>112.5838814799115</v>
+        <v>150.8229545603247</v>
       </c>
       <c r="D6" t="n">
-        <v>43.39128503230054</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>96.53721525399735</v>
+        <v>144.2069567814055</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>61.66848204226339</v>
+        <v>111.4038207394068</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>57.02187015806322</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.271003424101125</v>
+        <v>4.05363627083508</v>
       </c>
       <c r="C2" t="n">
-        <v>5.458517235612265</v>
+        <v>7.029313562407163</v>
       </c>
       <c r="D2" t="n">
-        <v>18.51085296357361</v>
+        <v>22.08245111162351</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.1762979806037</v>
+        <v>20.44980467946106</v>
       </c>
       <c r="C3" t="n">
-        <v>28.25960766674444</v>
+        <v>30.71397692736146</v>
       </c>
       <c r="D3" t="n">
-        <v>75.65838682778045</v>
+        <v>61.44268007028663</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.77613013236527</v>
+        <v>40.18980576875168</v>
       </c>
       <c r="C4" t="n">
-        <v>93.89533218186919</v>
+        <v>117.6722798310227</v>
       </c>
       <c r="D4" t="n">
-        <v>147.9326893190221</v>
+        <v>100.6340484238193</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.44862730977434</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="C5" t="n">
-        <v>138.2300767579509</v>
+        <v>184.077694546277</v>
       </c>
       <c r="D5" t="n">
-        <v>122.1785017935156</v>
+        <v>81.92684591939634</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.94851681768522</v>
+        <v>37.55479493055324</v>
       </c>
       <c r="C6" t="n">
-        <v>143.6179081588574</v>
+        <v>187.4519614057733</v>
       </c>
       <c r="D6" t="n">
-        <v>60.73974871404592</v>
+        <v>46.16864928761476</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.24273802932299</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="C7" t="n">
-        <v>129.4149641215188</v>
+        <v>180.1389227568388</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>92.87824156026949</v>
+        <v>148.3715305428204</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>55.69062027110455</v>
+        <v>91.41249223782897</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>37.43894870145212</v>
+        <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.088578277560466</v>
+        <v>2.438661297349077</v>
       </c>
       <c r="C2" t="n">
-        <v>2.457314503729767</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="D2" t="n">
-        <v>12.75584792127881</v>
+        <v>15.39674924570273</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.65735435568464</v>
+        <v>19.69385894719102</v>
       </c>
       <c r="C3" t="n">
-        <v>26.96860943565988</v>
+        <v>31.26866438026091</v>
       </c>
       <c r="D3" t="n">
-        <v>75.73201790559895</v>
+        <v>65.1585951308608</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.38347210839555</v>
+        <v>44.18453717733195</v>
       </c>
       <c r="C4" t="n">
-        <v>93.89533218186919</v>
+        <v>115.2984138821539</v>
       </c>
       <c r="D4" t="n">
-        <v>155.207439807491</v>
+        <v>107.9215616324434</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.55938487390499</v>
+        <v>41.20885988575987</v>
       </c>
       <c r="C5" t="n">
-        <v>168.4433623561465</v>
+        <v>220.2060100625596</v>
       </c>
       <c r="D5" t="n">
-        <v>131.8241729877405</v>
+        <v>86.46742905153783</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.6290068454485</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>176.7450209432575</v>
+        <v>226.2948093242983</v>
       </c>
       <c r="D6" t="n">
-        <v>59.29068910257763</v>
+        <v>45.76613272887356</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>131.2714490302495</v>
+        <v>190.2597598399191</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>71.01472018669303</v>
+        <v>112.4052033977386</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.689407872559513</v>
+        <v>3.258420630395164</v>
       </c>
       <c r="C2" t="n">
-        <v>9.196030745679874</v>
+        <v>12.19526998215388</v>
       </c>
       <c r="D2" t="n">
-        <v>12.01168316145973</v>
+        <v>14.82242683871834</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.25774198232718</v>
+        <v>14.23043297305752</v>
       </c>
       <c r="C3" t="n">
-        <v>17.79417713947344</v>
+        <v>21.98133109808609</v>
       </c>
       <c r="D3" t="n">
-        <v>69.01686360855078</v>
+        <v>63.01347639708153</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.1545039091278</v>
+        <v>41.47884050442774</v>
       </c>
       <c r="C4" t="n">
-        <v>81.1964256274367</v>
+        <v>98.00492807184634</v>
       </c>
       <c r="D4" t="n">
-        <v>157.28776319279</v>
+        <v>114.0731927472539</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.14400778401735</v>
+        <v>51.5908418581699</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1249162470721</v>
+        <v>218.389776809703</v>
       </c>
       <c r="D5" t="n">
-        <v>153.3980787885641</v>
+        <v>101.2672756930585</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.61770889908305</v>
+        <v>40.09064925062275</v>
       </c>
       <c r="C6" t="n">
-        <v>219.774041072691</v>
+        <v>282.1238560217017</v>
       </c>
       <c r="D6" t="n">
-        <v>81.67060976858792</v>
+        <v>58.04288777047993</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.78065365579224</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>187.984068661475</v>
+        <v>249.4277304794659</v>
       </c>
       <c r="D7" t="n">
-        <v>42.51949307092936</v>
+        <v>38.0279973240002</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>113.9907259400971</v>
+        <v>170.9860889101457</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>51.25312064790897</v>
+        <v>72.99686880156732</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.674280746368311</v>
+        <v>2.200096605217102</v>
       </c>
       <c r="C2" t="n">
-        <v>4.464006811210247</v>
+        <v>5.8787052530299</v>
       </c>
       <c r="D2" t="n">
-        <v>9.280461048245099</v>
+        <v>10.80806047605314</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.86856898081794</v>
+        <v>13.04742698944011</v>
       </c>
       <c r="C3" t="n">
-        <v>26.48264432205771</v>
+        <v>33.69848994827176</v>
       </c>
       <c r="D3" t="n">
-        <v>64.18666490365646</v>
+        <v>61.52121988662638</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.39400929123502</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="C4" t="n">
-        <v>67.08085713577607</v>
+        <v>82.30678228093984</v>
       </c>
       <c r="D4" t="n">
-        <v>156.981457909065</v>
+        <v>117.9020087938164</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.93631923907354</v>
+        <v>56.89227946110267</v>
       </c>
       <c r="C5" t="n">
-        <v>169.1551294417254</v>
+        <v>211.5911739577939</v>
       </c>
       <c r="D5" t="n">
-        <v>168.8360614378452</v>
+        <v>111.6247139728624</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.35231822376692</v>
+        <v>47.25544399621598</v>
       </c>
       <c r="C6" t="n">
-        <v>248.795484957931</v>
+        <v>316.7000284175701</v>
       </c>
       <c r="D6" t="n">
-        <v>96.96623900075323</v>
+        <v>68.34731167425446</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="C7" t="n">
-        <v>236.1927896785146</v>
+        <v>306.4397831604866</v>
       </c>
       <c r="D7" t="n">
-        <v>48.44826745687584</v>
+        <v>41.80085375142069</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>149.7067074205961</v>
+        <v>214.6296831024377</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>62.45780719647781</v>
+        <v>82.53749299143782</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.117850782238622</v>
+        <v>3.574543391162637</v>
       </c>
       <c r="C2" t="n">
-        <v>5.312236827679491</v>
+        <v>14.13225820263284</v>
       </c>
       <c r="D2" t="n">
-        <v>10.60876569209103</v>
+        <v>16.5748464907989</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.04113559258713</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="C3" t="n">
-        <v>22.19240685449915</v>
+        <v>28.78484268851648</v>
       </c>
       <c r="D3" t="n">
-        <v>58.31581363226054</v>
+        <v>56.68611244321084</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.5486834601495</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="C4" t="n">
-        <v>65.8045851202552</v>
+        <v>82.77900292668257</v>
       </c>
       <c r="D4" t="n">
-        <v>152.1188615299305</v>
+        <v>120.3652137837717</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.32272692391928</v>
+        <v>56.79410469067799</v>
       </c>
       <c r="C5" t="n">
-        <v>150.2810298275805</v>
+        <v>186.1884521104076</v>
       </c>
       <c r="D5" t="n">
-        <v>182.8505099159684</v>
+        <v>123.7002107350981</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.94479511551327</v>
+        <v>57.27810630887167</v>
       </c>
       <c r="C6" t="n">
-        <v>257.892359185482</v>
+        <v>325.434637742254</v>
       </c>
       <c r="D6" t="n">
-        <v>119.8694311931271</v>
+        <v>81.75111308033615</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.29128563518759</v>
+        <v>29.04500583014188</v>
       </c>
       <c r="C7" t="n">
-        <v>287.2760679735889</v>
+        <v>366.0269600697468</v>
       </c>
       <c r="D7" t="n">
-        <v>60.12615639889166</v>
+        <v>48.38838084691679</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>216.1317570899353</v>
+        <v>287.3133743863503</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>107.8312408436526</v>
+        <v>148.8781123582118</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>55.66018609227292</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.691772278595507</v>
+        <v>5.232715263635499</v>
       </c>
       <c r="C2" t="n">
-        <v>3.16711809390021</v>
+        <v>11.88012896909065</v>
       </c>
       <c r="D2" t="n">
-        <v>9.152833846693014</v>
+        <v>6.107452468119408</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.618722037853743</v>
+        <v>2.583959957577605</v>
       </c>
       <c r="C2" t="n">
-        <v>2.974695543867836</v>
+        <v>8.252571201898688</v>
       </c>
       <c r="D2" t="n">
-        <v>7.807839491874883</v>
+        <v>12.33075116533994</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90078672860884</v>
+        <v>14.27461161974862</v>
       </c>
       <c r="C3" t="n">
-        <v>25.11801501315465</v>
+        <v>40.40873550679871</v>
       </c>
       <c r="D3" t="n">
-        <v>63.30800070835556</v>
+        <v>62.16917337142927</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.74533610063513</v>
+        <v>42.97207876258713</v>
       </c>
       <c r="C4" t="n">
-        <v>93.06575537178064</v>
+        <v>117.5318899093154</v>
       </c>
       <c r="D4" t="n">
-        <v>157.7089329579119</v>
+        <v>122.892232374503</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.61981126321179</v>
+        <v>33.30579086657305</v>
       </c>
       <c r="C5" t="n">
-        <v>221.2859325372311</v>
+        <v>275.478405811655</v>
       </c>
       <c r="D5" t="n">
-        <v>169.2042168269378</v>
+        <v>113.9563647704485</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.50067563363265</v>
+        <v>18.03274183160542</v>
       </c>
       <c r="C6" t="n">
-        <v>242.2747167063237</v>
+        <v>301.6861607765236</v>
       </c>
       <c r="D6" t="n">
-        <v>93.18258334858602</v>
+        <v>66.97875537453442</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>151.9922160760827</v>
+        <v>202.057422001853</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>31.68001666834032</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>79.44302422765189</v>
+        <v>109.7348496421872</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>42.48905889209769</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.93801102591221</v>
+        <v>5.742242322139593</v>
       </c>
       <c r="C2" t="n">
-        <v>3.323215978875453</v>
+        <v>5.825690877000572</v>
       </c>
       <c r="D2" t="n">
-        <v>23.18888077430966</v>
+        <v>17.21003725544659</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.969647936626359</v>
+        <v>11.11829275059513</v>
       </c>
       <c r="C3" t="n">
-        <v>8.10432729855742</v>
+        <v>29.93348750248525</v>
       </c>
       <c r="D3" t="n">
-        <v>11.19192382841364</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3990828190242</v>
+        <v>13.39801560623912</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14813946430317</v>
+        <v>70.14255229148716</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576362684591082</v>
+        <v>1.576237130145779</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.202281084803848</v>
+        <v>3.989822670059037</v>
       </c>
       <c r="C2" t="n">
-        <v>4.636794407157685</v>
+        <v>3.25645713498667</v>
       </c>
       <c r="D2" t="n">
-        <v>28.31556728588651</v>
+        <v>16.63473310075796</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.31450342272425</v>
+        <v>16.35100801423063</v>
       </c>
       <c r="C3" t="n">
-        <v>11.27537238327462</v>
+        <v>25.41744806294992</v>
       </c>
       <c r="D3" t="n">
-        <v>27.96508335547039</v>
+        <v>20.72469403665017</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.69065166217102</v>
+        <v>12.99244911800229</v>
       </c>
       <c r="C4" t="n">
-        <v>12.89034735676062</v>
+        <v>46.16275880138927</v>
       </c>
       <c r="D4" t="n">
-        <v>20.930861054542</v>
+        <v>19.39933463591698</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44350206053287</v>
+        <v>15.4394046814356</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15848517981495</v>
+        <v>86.13562611748283</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25126359169113</v>
+        <v>3.25040098556539</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.223879534297278</v>
+        <v>4.541564879845745</v>
       </c>
       <c r="C2" t="n">
-        <v>7.565347808925921</v>
+        <v>8.526478811383548</v>
       </c>
       <c r="D2" t="n">
-        <v>25.24367871929824</v>
+        <v>14.96478025583413</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.15251505152352</v>
+        <v>14.92256510455152</v>
       </c>
       <c r="C3" t="n">
-        <v>15.37907778702628</v>
+        <v>17.68618489200629</v>
       </c>
       <c r="D3" t="n">
-        <v>44.12955930589413</v>
+        <v>29.22172041690631</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.05321966467436</v>
+        <v>23.61103228713579</v>
       </c>
       <c r="C4" t="n">
-        <v>21.91359050649305</v>
+        <v>56.47503668679776</v>
       </c>
       <c r="D4" t="n">
-        <v>30.23488404768902</v>
+        <v>25.4233385491754</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.70104997629023</v>
+        <v>11.53553552490002</v>
       </c>
       <c r="C5" t="n">
-        <v>15.83068173097982</v>
+        <v>50.87907477259096</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73988753003033</v>
+        <v>16.73104555560881</v>
       </c>
       <c r="C21" t="n">
-        <v>102.113313933185</v>
+        <v>102.0593778892138</v>
       </c>
       <c r="D21" t="n">
-        <v>5.0219662590091</v>
+        <v>4.182761388902203</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.630323083855457</v>
+        <v>5.586144437164351</v>
       </c>
       <c r="C2" t="n">
-        <v>6.924266558052754</v>
+        <v>10.00499085397924</v>
       </c>
       <c r="D2" t="n">
-        <v>20.56466916085794</v>
+        <v>17.94536628592745</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.01507037292897</v>
+        <v>15.27599427808037</v>
       </c>
       <c r="C3" t="n">
-        <v>23.59630607157209</v>
+        <v>26.56609287691869</v>
       </c>
       <c r="D3" t="n">
-        <v>53.50034114292993</v>
+        <v>34.09118902997049</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.41356212986194</v>
+        <v>26.59750880345459</v>
       </c>
       <c r="C4" t="n">
-        <v>31.34524070119216</v>
+        <v>49.65974412391641</v>
       </c>
       <c r="D4" t="n">
-        <v>44.42702886028091</v>
+        <v>33.85949657176824</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.39643045053324</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="C5" t="n">
-        <v>29.37880004958581</v>
+        <v>79.25158342532377</v>
       </c>
       <c r="D5" t="n">
-        <v>34.18936380039518</v>
+        <v>31.78408192499049</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>18.91827826083604</v>
+        <v>48.30198704894308</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07137851900765</v>
+        <v>18.05485822166016</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8942312906689</v>
+        <v>117.7864560174972</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884334673907674</v>
+        <v>6.018286073886719</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.98964274360979</v>
+        <v>5.558655501445441</v>
       </c>
       <c r="C2" t="n">
-        <v>6.073091298470769</v>
+        <v>7.83925541841078</v>
       </c>
       <c r="D2" t="n">
-        <v>31.29517156827557</v>
+        <v>20.80814259151115</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.76825078853552</v>
+        <v>15.53615741970577</v>
       </c>
       <c r="C3" t="n">
-        <v>24.01354884587698</v>
+        <v>31.58282364561989</v>
       </c>
       <c r="D3" t="n">
-        <v>53.84395283941632</v>
+        <v>37.76783418237479</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.13430381349934</v>
+        <v>20.44587768864407</v>
       </c>
       <c r="C4" t="n">
-        <v>39.51338160052563</v>
+        <v>49.44277788127786</v>
       </c>
       <c r="D4" t="n">
-        <v>52.28886447588937</v>
+        <v>37.34371917414018</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.50027472300515</v>
+        <v>19.5613230071177</v>
       </c>
       <c r="C5" t="n">
-        <v>33.23215978875454</v>
+        <v>63.34727061652545</v>
       </c>
       <c r="D5" t="n">
-        <v>34.45934441906305</v>
+        <v>29.37880004958581</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.91449013873929</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>22.86294053649972</v>
+        <v>60.25672884355649</v>
       </c>
       <c r="D6" t="n">
-        <v>31.15478164656829</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>15.81006502919063</v>
+        <v>29.34443887993716</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
         <v>30.0414797499524</v>
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.066271714541922</v>
+        <v>7.055472519140705</v>
       </c>
       <c r="C21" t="n">
-        <v>66.24629732383052</v>
+        <v>66.14505486694411</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299703785906441</v>
+        <v>4.40967032446294</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.43888228152733</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C2" t="n">
-        <v>5.155157195000002</v>
+        <v>4.85376064979623</v>
       </c>
       <c r="D2" t="n">
-        <v>31.6731444344106</v>
+        <v>18.6846223072253</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.64968030049991</v>
+        <v>18.0052528958865</v>
       </c>
       <c r="C3" t="n">
-        <v>23.84174299763379</v>
+        <v>30.96923133046564</v>
       </c>
       <c r="D3" t="n">
-        <v>67.85349257901831</v>
+        <v>46.11759840699392</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.54569715930776</v>
+        <v>26.7634241654723</v>
       </c>
       <c r="C4" t="n">
-        <v>52.77384784178729</v>
+        <v>68.16568834896879</v>
       </c>
       <c r="D4" t="n">
-        <v>69.21223140169589</v>
+        <v>48.11545498513618</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.48326621686347</v>
+        <v>26.28629478120835</v>
       </c>
       <c r="C5" t="n">
-        <v>57.97220193577417</v>
+        <v>80.60148651866314</v>
       </c>
       <c r="D5" t="n">
-        <v>46.73119072214818</v>
+        <v>37.03643214271093</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.89690079552086</v>
+        <v>20.04532462531138</v>
       </c>
       <c r="C6" t="n">
-        <v>40.57366912111219</v>
+        <v>83.64294090641977</v>
       </c>
       <c r="D6" t="n">
-        <v>35.26045054572845</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.59992996275281</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>26.29022177202533</v>
+        <v>63.59957977651686</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>20.44489594093983</v>
+        <v>30.70906818884022</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.18387422479719</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.292359739057018</v>
+        <v>7.277384539921094</v>
       </c>
       <c r="C21" t="n">
-        <v>76.56977726009869</v>
+        <v>75.50286460168135</v>
       </c>
       <c r="D21" t="n">
-        <v>6.38081477167489</v>
+        <v>5.458038404940821</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.053055433758333</v>
+        <v>4.621086443889737</v>
       </c>
       <c r="C2" t="n">
-        <v>4.059526757060561</v>
+        <v>9.719302272043423</v>
       </c>
       <c r="D2" t="n">
-        <v>27.61950816357552</v>
+        <v>17.31508425980099</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24716374175872</v>
+        <v>19.32570355809846</v>
       </c>
       <c r="C3" t="n">
-        <v>21.52481841561132</v>
+        <v>23.6404847182632</v>
       </c>
       <c r="D3" t="n">
-        <v>77.44516764950964</v>
+        <v>50.36365722786137</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.8422260237193</v>
+        <v>31.62602054460675</v>
       </c>
       <c r="C4" t="n">
-        <v>56.9727827728509</v>
+        <v>73.74299705679491</v>
       </c>
       <c r="D4" t="n">
-        <v>87.0162260182118</v>
+        <v>60.43147993491241</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.14089830998859</v>
+        <v>33.72303364087794</v>
       </c>
       <c r="C5" t="n">
-        <v>80.99418560036187</v>
+        <v>106.5441696033851</v>
       </c>
       <c r="D5" t="n">
-        <v>61.87464906015524</v>
+        <v>45.67581194008286</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.80509953740717</v>
+        <v>28.6591789823729</v>
       </c>
       <c r="C6" t="n">
-        <v>68.99133816824036</v>
+        <v>107.4719211838983</v>
       </c>
       <c r="D6" t="n">
-        <v>42.30449032369931</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="C7" t="n">
-        <v>44.6155244194963</v>
+        <v>95.75868932452963</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>28.78975142703771</v>
+        <v>60.16640805476577</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>25.18281036163492</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6524,7 +6524,7 @@
         <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.506489184641604</v>
+        <v>7.486602366484065</v>
       </c>
       <c r="C21" t="n">
-        <v>86.32462562337845</v>
+        <v>84.22427662294574</v>
       </c>
       <c r="D21" t="n">
-        <v>7.506489184641604</v>
+        <v>6.550777070673557</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_36_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497647746983</v>
+        <v>10.84497650009927</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907244804643</v>
+        <v>37.78907252689817</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.964117303299373</v>
+        <v>0.8845546815263761</v>
       </c>
       <c r="C2" t="n">
-        <v>6.640541471525426</v>
+        <v>3.784637399871454</v>
       </c>
       <c r="D2" t="n">
-        <v>16.47176298185299</v>
+        <v>16.21356333563607</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.37202562664731</v>
+        <v>8.811185645615124</v>
       </c>
       <c r="C3" t="n">
-        <v>31.43065275146164</v>
+        <v>47.47241023885451</v>
       </c>
       <c r="D3" t="n">
-        <v>52.1111681414207</v>
+        <v>65.12914269973339</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.34447993766616</v>
+        <v>16.38733267928776</v>
       </c>
       <c r="C4" t="n">
-        <v>65.12816095202915</v>
+        <v>131.3666785575614</v>
       </c>
       <c r="D4" t="n">
-        <v>70.19496085364693</v>
+        <v>68.80382435672921</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.86524818927349</v>
+        <v>14.5298660228528</v>
       </c>
       <c r="C5" t="n">
-        <v>122.2521328713341</v>
+        <v>132.7322896141688</v>
       </c>
       <c r="D5" t="n">
-        <v>56.47503668679778</v>
+        <v>43.34416114249668</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.07177506006381</v>
+        <v>9.418887474543901</v>
       </c>
       <c r="C6" t="n">
-        <v>139.2304776685784</v>
+        <v>77.52468921355364</v>
       </c>
       <c r="D6" t="n">
-        <v>43.23027840880406</v>
+        <v>29.06169554111408</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.87101550231194</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>125.5223344741802</v>
+        <v>37.30935800449154</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>94.54721265748907</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>53.13905798776709</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.6814867953624</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.13802739376909</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.6814867953624</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.032258805519903</v>
+        <v>0.7009678608322226</v>
       </c>
       <c r="C2" t="n">
-        <v>12.03328161095315</v>
+        <v>11.63960078155018</v>
       </c>
       <c r="D2" t="n">
-        <v>15.30348321379928</v>
+        <v>19.14113498970006</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.75138115111408</v>
+        <v>5.713771638716437</v>
       </c>
       <c r="C3" t="n">
-        <v>28.36759991421159</v>
+        <v>28.67685044104933</v>
       </c>
       <c r="D3" t="n">
-        <v>52.71985171805372</v>
+        <v>62.96438901186919</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.32346232524949</v>
+        <v>16.93612964596173</v>
       </c>
       <c r="C4" t="n">
-        <v>71.72648727227197</v>
+        <v>124.359945192352</v>
       </c>
       <c r="D4" t="n">
-        <v>78.70769519717103</v>
+        <v>85.03800439415447</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.52854978444584</v>
+        <v>19.58586669972387</v>
       </c>
       <c r="C5" t="n">
-        <v>119.8959383811417</v>
+        <v>193.3797540440155</v>
       </c>
       <c r="D5" t="n">
-        <v>66.26797003665972</v>
+        <v>57.38315331322608</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.36361617013237</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>165.4745572985042</v>
+        <v>146.0732591671787</v>
       </c>
       <c r="D6" t="n">
-        <v>50.2340665309008</v>
+        <v>35.50196048097316</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.61446055633404</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>160.1966816404733</v>
+        <v>74.31928295918779</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.36144738607885</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>129.0949143699343</v>
+        <v>38.7201294554942</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>82.42655550085793</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.861393332066825</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2154391503604</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.844067498575178</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.275151399096364</v>
+        <v>0.3809181092477624</v>
       </c>
       <c r="C2" t="n">
-        <v>13.44798005277281</v>
+        <v>5.003968048545993</v>
       </c>
       <c r="D2" t="n">
-        <v>28.84472929847554</v>
+        <v>13.03662776469339</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.59215809657685</v>
+        <v>4.913647259755287</v>
       </c>
       <c r="C3" t="n">
-        <v>37.11497195905067</v>
+        <v>38.39615271309275</v>
       </c>
       <c r="D3" t="n">
-        <v>52.81311774995717</v>
+        <v>65.28131359389165</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.66805576944012</v>
+        <v>18.21240166148258</v>
       </c>
       <c r="C4" t="n">
-        <v>70.41192709628548</v>
+        <v>115.7706345278966</v>
       </c>
       <c r="D4" t="n">
-        <v>83.95317318096176</v>
+        <v>94.83977347335463</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.5411325781518</v>
+        <v>19.38951715887451</v>
       </c>
       <c r="C5" t="n">
-        <v>123.8474728907351</v>
+        <v>229.925312334603</v>
       </c>
       <c r="D5" t="n">
-        <v>75.86455384567229</v>
+        <v>64.84443586550184</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.80388110999145</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>176.8255242550058</v>
+        <v>185.8418951708085</v>
       </c>
       <c r="D6" t="n">
-        <v>57.9623844587317</v>
+        <v>36.38749691020379</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.57937968088841</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>193.0744305079947</v>
+        <v>70.12722026205391</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.45457454926205</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>164.6439987407113</v>
+        <v>38.63668090063322</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.64374875654542</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>116.3734276183041</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>67.90257996423065</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>42.11403126907541</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.025718301366755</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.350411856122</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.03214787670844</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.539822368615503</v>
+        <v>1.030835089459151</v>
       </c>
       <c r="C2" t="n">
-        <v>9.143998117354792</v>
+        <v>6.3715426005618</v>
       </c>
       <c r="D2" t="n">
-        <v>23.58256160371263</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.01354884587698</v>
+        <v>3.05323536020758</v>
       </c>
       <c r="C3" t="n">
-        <v>54.87478792887547</v>
+        <v>28.13198046519235</v>
       </c>
       <c r="D3" t="n">
-        <v>58.0801941832413</v>
+        <v>60.7750916313988</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.83250635766807</v>
+        <v>14.14109393197106</v>
       </c>
       <c r="C4" t="n">
-        <v>100.3532685804047</v>
+        <v>105.2413903998496</v>
       </c>
       <c r="D4" t="n">
-        <v>82.06429059799088</v>
+        <v>104.8967969556589</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.18245050873644</v>
+        <v>23.26742059064941</v>
       </c>
       <c r="C5" t="n">
-        <v>105.660596669563</v>
+        <v>225.9737778250096</v>
       </c>
       <c r="D5" t="n">
-        <v>55.02695882303374</v>
+        <v>82.66315669758144</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.40508625342222</v>
+        <v>17.67047692873834</v>
       </c>
       <c r="C6" t="n">
-        <v>127.1549809063427</v>
+        <v>272.101193709046</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>45.96739100824416</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>115.7608170508541</v>
+        <v>160.4362280803095</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>85.78511439708629</v>
+        <v>62.50296759087318</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>51.80780810080841</v>
+        <v>36.27655941962388</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.524875168873549</v>
+        <v>0.5586144437164351</v>
       </c>
       <c r="C2" t="n">
-        <v>4.35503281603885</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68774747678728</v>
+        <v>11.97634024410684</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.56471021858694</v>
+        <v>3.308489763311751</v>
       </c>
       <c r="C3" t="n">
-        <v>46.04396732917541</v>
+        <v>27.0716929446058</v>
       </c>
       <c r="D3" t="n">
-        <v>62.87112297996573</v>
+        <v>59.92097112870407</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.67256359733385</v>
+        <v>11.14185469549705</v>
       </c>
       <c r="C4" t="n">
-        <v>120.6459936271863</v>
+        <v>91.90434783765667</v>
       </c>
       <c r="D4" t="n">
-        <v>91.72566975548375</v>
+        <v>110.3592411820882</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.79037332184348</v>
+        <v>24.07736244665303</v>
       </c>
       <c r="C5" t="n">
-        <v>144.5623494503429</v>
+        <v>220.6477965294707</v>
       </c>
       <c r="D5" t="n">
-        <v>67.22517404830035</v>
+        <v>96.57943040527999</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.35603992593888</v>
+        <v>21.69564251615027</v>
       </c>
       <c r="C6" t="n">
-        <v>150.8229545603247</v>
+        <v>316.4987701381995</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>54.90325861229863</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>144.2069567814055</v>
+        <v>238.4085942469997</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>111.4038207394068</v>
+        <v>99.05343461998193</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>45.04062117543515</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>35.01894061048373</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.05363627083508</v>
+        <v>0.4427682146153115</v>
       </c>
       <c r="C2" t="n">
-        <v>7.029313562407163</v>
+        <v>8.102363803148926</v>
       </c>
       <c r="D2" t="n">
-        <v>22.08245111162351</v>
+        <v>12.07156977141878</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.44980467946106</v>
+        <v>2.611448893296516</v>
       </c>
       <c r="C3" t="n">
-        <v>30.71397692736146</v>
+        <v>20.07183181332604</v>
       </c>
       <c r="D3" t="n">
-        <v>61.44268007028663</v>
+        <v>55.98416283467436</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.18980576875168</v>
+        <v>8.921141388490765</v>
       </c>
       <c r="C4" t="n">
-        <v>117.6722798310227</v>
+        <v>80.07330625377834</v>
       </c>
       <c r="D4" t="n">
-        <v>100.6340484238193</v>
+        <v>113.9710909860122</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.25165587411923</v>
+        <v>21.25483779694345</v>
       </c>
       <c r="C5" t="n">
-        <v>184.077694546277</v>
+        <v>198.779366417373</v>
       </c>
       <c r="D5" t="n">
-        <v>81.92684591939634</v>
+        <v>110.274810879523</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.55479493055324</v>
+        <v>26.20382797405162</v>
       </c>
       <c r="C6" t="n">
-        <v>187.4519614057733</v>
+        <v>332.3579225526025</v>
       </c>
       <c r="D6" t="n">
-        <v>46.16864928761476</v>
+        <v>68.06555008313562</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>180.1389227568388</v>
+        <v>334.0475103516112</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>44.79518424937346</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>148.3715305428204</v>
+        <v>185.8399316754</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>40.88979188187965</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>91.41249223782897</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.438661297349077</v>
+        <v>0.3072870314292516</v>
       </c>
       <c r="C2" t="n">
-        <v>3.337942194439155</v>
+        <v>4.408047192068178</v>
       </c>
       <c r="D2" t="n">
-        <v>15.39674924570273</v>
+        <v>8.787623700713199</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.69385894719102</v>
+        <v>3.475386873033709</v>
       </c>
       <c r="C3" t="n">
-        <v>31.26866438026091</v>
+        <v>26.93915700453248</v>
       </c>
       <c r="D3" t="n">
-        <v>65.1585951308608</v>
+        <v>60.61310326019807</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.18453717733195</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="C4" t="n">
-        <v>115.2984138821539</v>
+        <v>113.652022982132</v>
       </c>
       <c r="D4" t="n">
-        <v>107.9215616324434</v>
+        <v>116.0514143713112</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.20885988575987</v>
+        <v>15.73250696055514</v>
       </c>
       <c r="C5" t="n">
-        <v>220.2060100625596</v>
+        <v>286.4985237918255</v>
       </c>
       <c r="D5" t="n">
-        <v>86.46742905153783</v>
+        <v>100.3837027592364</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>9.137125883425066</v>
       </c>
       <c r="C6" t="n">
-        <v>226.2948093242983</v>
+        <v>294.9238825896716</v>
       </c>
       <c r="D6" t="n">
-        <v>45.76613272887356</v>
+        <v>59.37119241432587</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>190.2597598399191</v>
+        <v>130.6725829306589</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>112.4052033977386</v>
+        <v>55.99398031171682</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.258420630395164</v>
+        <v>0.1678788574262046</v>
       </c>
       <c r="C2" t="n">
-        <v>12.19526998215388</v>
+        <v>2.097013096271187</v>
       </c>
       <c r="D2" t="n">
-        <v>14.82242683871834</v>
+        <v>6.730862260316131</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.23043297305752</v>
+        <v>2.282563412373834</v>
       </c>
       <c r="C3" t="n">
-        <v>21.98133109808609</v>
+        <v>21.76043786463055</v>
       </c>
       <c r="D3" t="n">
-        <v>63.01347639708153</v>
+        <v>54.08448102695678</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.47884050442774</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C4" t="n">
-        <v>98.00492807184634</v>
+        <v>87.32253130193681</v>
       </c>
       <c r="D4" t="n">
-        <v>114.0731927472539</v>
+        <v>114.2518708294268</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.5908418581699</v>
+        <v>14.75075925630833</v>
       </c>
       <c r="C5" t="n">
-        <v>218.389776809703</v>
+        <v>224.3538941130024</v>
       </c>
       <c r="D5" t="n">
-        <v>101.2672756930585</v>
+        <v>104.3843246540421</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.09064925062275</v>
+        <v>8.895615948180351</v>
       </c>
       <c r="C6" t="n">
-        <v>282.1238560217017</v>
+        <v>303.135220387992</v>
       </c>
       <c r="D6" t="n">
-        <v>58.04288777047993</v>
+        <v>62.43031826075894</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>3.114103717870883</v>
       </c>
       <c r="C7" t="n">
-        <v>249.4277304794659</v>
+        <v>181.8756344456513</v>
       </c>
       <c r="D7" t="n">
-        <v>38.0279973240002</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>170.9860889101457</v>
+        <v>65.75746123045136</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>72.99686880156732</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.200096605217102</v>
+        <v>0.4732023934469626</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8787052530299</v>
+        <v>2.545671797111979</v>
       </c>
       <c r="D2" t="n">
-        <v>10.80806047605314</v>
+        <v>11.31758753455723</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.04742698944011</v>
+        <v>1.354811831860598</v>
       </c>
       <c r="C3" t="n">
-        <v>33.69848994827176</v>
+        <v>13.88682127657113</v>
       </c>
       <c r="D3" t="n">
-        <v>61.52121988662638</v>
+        <v>47.16806845053801</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.01188845010475</v>
+        <v>7.223699607848031</v>
       </c>
       <c r="C4" t="n">
-        <v>82.30678228093984</v>
+        <v>69.81207924899068</v>
       </c>
       <c r="D4" t="n">
-        <v>117.9020087938164</v>
+        <v>115.5791937255685</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.89227946110267</v>
+        <v>15.2661768010379</v>
       </c>
       <c r="C5" t="n">
-        <v>211.5911739577939</v>
+        <v>190.9744721686108</v>
       </c>
       <c r="D5" t="n">
-        <v>111.6247139728624</v>
+        <v>121.1231230114503</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.25544399621598</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C6" t="n">
-        <v>316.7000284175701</v>
+        <v>331.6333927468684</v>
       </c>
       <c r="D6" t="n">
-        <v>68.34731167425446</v>
+        <v>79.29576207201488</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.69029180927252</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>306.4397831604866</v>
+        <v>312.7877638161465</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>214.6296831024377</v>
+        <v>150.9584357435108</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>82.53749299143782</v>
+        <v>53.58280795008665</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.574543391162637</v>
+        <v>0.755945732270044</v>
       </c>
       <c r="C2" t="n">
-        <v>14.13225820263284</v>
+        <v>4.571999058677396</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5748464907989</v>
+        <v>9.36292785540183</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.39179944945249</v>
+        <v>1.462804079327747</v>
       </c>
       <c r="C3" t="n">
-        <v>28.78484268851648</v>
+        <v>11.72206758870692</v>
       </c>
       <c r="D3" t="n">
-        <v>56.68611244321084</v>
+        <v>45.27820411986289</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.24313893995049</v>
+        <v>4.951935420220911</v>
       </c>
       <c r="C4" t="n">
-        <v>82.77900292668257</v>
+        <v>51.85493199061228</v>
       </c>
       <c r="D4" t="n">
-        <v>120.3652137837717</v>
+        <v>112.1077338433518</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.79410469067799</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="C5" t="n">
-        <v>186.1884521104076</v>
+        <v>160.3194001035042</v>
       </c>
       <c r="D5" t="n">
-        <v>123.7002107350981</v>
+        <v>133.9349305518711</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.27810630887167</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C6" t="n">
-        <v>325.434637742254</v>
+        <v>320.040915855122</v>
       </c>
       <c r="D6" t="n">
-        <v>81.75111308033615</v>
+        <v>96.56372244201204</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.04500583014188</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>366.0269600697468</v>
+        <v>389.2030781239012</v>
       </c>
       <c r="D7" t="n">
-        <v>48.38838084691679</v>
+        <v>52.58044354405067</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>287.3133743863503</v>
+        <v>273.7112599440107</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>148.8781123582118</v>
+        <v>114.0437403161264</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>24.51718541815559</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>55.66018609227292</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.232715263635499</v>
+        <v>2.321833320543707</v>
       </c>
       <c r="C2" t="n">
-        <v>11.88012896909065</v>
+        <v>5.445754515457057</v>
       </c>
       <c r="D2" t="n">
-        <v>6.107452468119408</v>
+        <v>6.482480091141689</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.583959957577605</v>
+        <v>0.6214462967882309</v>
       </c>
       <c r="C2" t="n">
-        <v>8.252571201898688</v>
+        <v>7.290458451736814</v>
       </c>
       <c r="D2" t="n">
-        <v>12.33075116533994</v>
+        <v>11.07116886079128</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.27461161974862</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C3" t="n">
-        <v>40.40873550679871</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="D3" t="n">
-        <v>62.16917337142927</v>
+        <v>42.49985811684442</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.97207876258713</v>
+        <v>3.879866927183394</v>
       </c>
       <c r="C4" t="n">
-        <v>117.5318899093154</v>
+        <v>41.32568786256524</v>
       </c>
       <c r="D4" t="n">
-        <v>122.892232374503</v>
+        <v>109.5551898123101</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.30579086657305</v>
+        <v>10.99557428756428</v>
       </c>
       <c r="C5" t="n">
-        <v>275.478405811655</v>
+        <v>129.8361338866407</v>
       </c>
       <c r="D5" t="n">
-        <v>113.9563647704485</v>
+        <v>141.6171063376024</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.03274183160542</v>
+        <v>17.54972196111598</v>
       </c>
       <c r="C6" t="n">
-        <v>301.6861607765236</v>
+        <v>293.5553262899516</v>
       </c>
       <c r="D6" t="n">
-        <v>66.97875537453442</v>
+        <v>110.8933119331985</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>14.9117658798048</v>
       </c>
       <c r="C7" t="n">
-        <v>202.057422001853</v>
+        <v>420.1644554727329</v>
       </c>
       <c r="D7" t="n">
-        <v>31.68001666834032</v>
+        <v>64.4978789259027</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>109.7348496421872</v>
+        <v>378.8564390688441</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48905889209769</v>
+        <v>207.0093574220739</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>78.29437941368313</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.60978849752428</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.742242322139593</v>
+        <v>4.624031687002477</v>
       </c>
       <c r="C2" t="n">
-        <v>5.825690877000572</v>
+        <v>13.00423009045325</v>
       </c>
       <c r="D2" t="n">
-        <v>17.21003725544659</v>
+        <v>11.13301896615883</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.11829275059513</v>
+        <v>3.848451000647497</v>
       </c>
       <c r="C3" t="n">
-        <v>29.93348750248525</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D3" t="n">
-        <v>8.266315669758143</v>
+        <v>7.480917506360695</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.44074796594459</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39801560623912</v>
+        <v>11.6790412383332</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14255229148716</v>
+        <v>59.95241169011044</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576237130145779</v>
+        <v>0.7786027492222135</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.989822670059037</v>
+        <v>3.2319134423805</v>
       </c>
       <c r="C2" t="n">
-        <v>3.25645713498667</v>
+        <v>7.015569094547707</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63473310075796</v>
+        <v>23.43529944807561</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35100801423063</v>
+        <v>11.49135687820892</v>
       </c>
       <c r="C3" t="n">
-        <v>25.41744806294992</v>
+        <v>37.41931374736718</v>
       </c>
       <c r="D3" t="n">
-        <v>20.72469403665017</v>
+        <v>15.39871274111122</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.99244911800229</v>
+        <v>4.977460860531329</v>
       </c>
       <c r="C4" t="n">
-        <v>46.16275880138927</v>
+        <v>18.04648629946487</v>
       </c>
       <c r="D4" t="n">
-        <v>19.39933463591698</v>
+        <v>18.0975371800857</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4394046814356</v>
+        <v>13.63258129683203</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13562611748283</v>
+        <v>73.77632231226745</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25040098556539</v>
+        <v>1.603833093744945</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.541564879845745</v>
+        <v>1.841758693167016</v>
       </c>
       <c r="C2" t="n">
-        <v>8.526478811383548</v>
+        <v>6.179120050529424</v>
       </c>
       <c r="D2" t="n">
-        <v>14.96478025583413</v>
+        <v>20.53619847743478</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.92256510455152</v>
+        <v>11.41772580039041</v>
       </c>
       <c r="C3" t="n">
-        <v>17.68618489200629</v>
+        <v>30.96923133046564</v>
       </c>
       <c r="D3" t="n">
-        <v>29.22172041690631</v>
+        <v>31.36193041216436</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.61103228713579</v>
+        <v>15.35355234671587</v>
       </c>
       <c r="C4" t="n">
-        <v>56.47503668679776</v>
+        <v>65.58761887761666</v>
       </c>
       <c r="D4" t="n">
-        <v>25.4233385491754</v>
+        <v>21.96464138711389</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.53553552490002</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C5" t="n">
-        <v>50.87907477259096</v>
+        <v>22.31021657900877</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>26.26175108860219</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>24.11663235482289</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73104555560881</v>
+        <v>14.84511122634742</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0593778892138</v>
+        <v>87.42121055515702</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182761388902203</v>
+        <v>2.474185204391236</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.586144437164351</v>
+        <v>2.319869825135213</v>
       </c>
       <c r="C2" t="n">
-        <v>10.00499085397924</v>
+        <v>8.068002633500289</v>
       </c>
       <c r="D2" t="n">
-        <v>17.94536628592745</v>
+        <v>20.31628699168349</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.27599427808037</v>
+        <v>8.546113765468485</v>
       </c>
       <c r="C3" t="n">
-        <v>26.56609287691869</v>
+        <v>26.71826377107694</v>
       </c>
       <c r="D3" t="n">
-        <v>34.09118902997049</v>
+        <v>40.51181901574463</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.59750880345459</v>
+        <v>19.4376227963826</v>
       </c>
       <c r="C4" t="n">
-        <v>49.65974412391641</v>
+        <v>72.8240812056199</v>
       </c>
       <c r="D4" t="n">
-        <v>33.85949657176824</v>
+        <v>32.51941095547134</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.36559536107409</v>
+        <v>14.65258448588365</v>
       </c>
       <c r="C5" t="n">
-        <v>79.25158342532377</v>
+        <v>79.64428250702251</v>
       </c>
       <c r="D5" t="n">
-        <v>31.78408192499049</v>
+        <v>28.51977080836985</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.86794708601219</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>48.30198704894308</v>
+        <v>24.35225180384214</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05485822166016</v>
+        <v>16.09006952542146</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7864560174972</v>
+        <v>101.6214917395039</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018286073886719</v>
+        <v>3.387383057983465</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.558655501445441</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="C2" t="n">
-        <v>7.83925541841078</v>
+        <v>12.06666103289755</v>
       </c>
       <c r="D2" t="n">
-        <v>20.80814259151115</v>
+        <v>22.59983215176158</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.53615741970577</v>
+        <v>8.217228284545802</v>
       </c>
       <c r="C3" t="n">
-        <v>31.58282364561989</v>
+        <v>29.35425635697963</v>
       </c>
       <c r="D3" t="n">
-        <v>37.76783418237479</v>
+        <v>46.94226647856124</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.44587768864407</v>
+        <v>17.99543541884404</v>
       </c>
       <c r="C4" t="n">
-        <v>49.44277788127786</v>
+        <v>68.80382435672921</v>
       </c>
       <c r="D4" t="n">
-        <v>37.34371917414018</v>
+        <v>44.80991046493716</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.5613230071177</v>
+        <v>21.89297380470387</v>
       </c>
       <c r="C5" t="n">
-        <v>63.34727061652545</v>
+        <v>109.8575681052181</v>
       </c>
       <c r="D5" t="n">
-        <v>29.37880004958581</v>
+        <v>33.25670348136071</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55222523587222</v>
+        <v>12.88052987971816</v>
       </c>
       <c r="C6" t="n">
-        <v>60.25672884355649</v>
+        <v>78.12846405166543</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>35.46170882509904</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>29.34443887993716</v>
+        <v>26.82920126165683</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.2611134982632</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055472519140705</v>
+        <v>17.36044520903806</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14505486694411</v>
+        <v>115.4469606401031</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40967032446294</v>
+        <v>4.340111302259515</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.868887775987432</v>
+        <v>1.812306262039612</v>
       </c>
       <c r="C2" t="n">
-        <v>4.85376064979623</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="D2" t="n">
-        <v>18.6846223072253</v>
+        <v>29.52900744833556</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.0052528958865</v>
+        <v>7.981608835526568</v>
       </c>
       <c r="C3" t="n">
-        <v>30.96923133046564</v>
+        <v>38.82321296444012</v>
       </c>
       <c r="D3" t="n">
-        <v>46.11759840699392</v>
+        <v>53.22054304721959</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.7634241654723</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C4" t="n">
-        <v>68.16568834896879</v>
+        <v>71.1904530257532</v>
       </c>
       <c r="D4" t="n">
-        <v>48.11545498513618</v>
+        <v>56.79410469067798</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.28629478120835</v>
+        <v>24.59277999138261</v>
       </c>
       <c r="C5" t="n">
-        <v>80.60148651866314</v>
+        <v>118.5460352878024</v>
       </c>
       <c r="D5" t="n">
-        <v>37.03643214271093</v>
+        <v>40.54618018539328</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.04532462531138</v>
+        <v>20.7296027751714</v>
       </c>
       <c r="C6" t="n">
-        <v>83.64294090641977</v>
+        <v>124.5386232745249</v>
       </c>
       <c r="D6" t="n">
-        <v>33.6906359666378</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>63.59957977651686</v>
+        <v>68.86960145291374</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>30.70906818884022</v>
+        <v>30.62561963397925</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.277384539921094</v>
+        <v>17.7607159631457</v>
       </c>
       <c r="C21" t="n">
-        <v>75.50286460168135</v>
+        <v>128.7651907328063</v>
       </c>
       <c r="D21" t="n">
-        <v>5.458038404940821</v>
+        <v>5.328214788943709</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.621086443889737</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C2" t="n">
-        <v>9.719302272043423</v>
+        <v>9.216647447469056</v>
       </c>
       <c r="D2" t="n">
-        <v>17.31508425980099</v>
+        <v>23.11819493960389</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.32570355809846</v>
+        <v>10.99066554904304</v>
       </c>
       <c r="C3" t="n">
-        <v>23.6404847182632</v>
+        <v>59.4644584462293</v>
       </c>
       <c r="D3" t="n">
-        <v>50.36365722786137</v>
+        <v>59.69026041820607</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.62602054460675</v>
+        <v>11.80551614356789</v>
       </c>
       <c r="C4" t="n">
-        <v>73.74299705679491</v>
+        <v>103.5949994998277</v>
       </c>
       <c r="D4" t="n">
-        <v>60.43147993491241</v>
+        <v>52.67174608054562</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.72303364087794</v>
+        <v>11.65825398793088</v>
       </c>
       <c r="C5" t="n">
-        <v>106.5441696033851</v>
+        <v>74.41647598190823</v>
       </c>
       <c r="D5" t="n">
-        <v>45.67581194008286</v>
+        <v>34.80295611554943</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.6591789823729</v>
+        <v>6.802529842726151</v>
       </c>
       <c r="C6" t="n">
-        <v>107.4719211838983</v>
+        <v>45.36361617013237</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>25.27803988894688</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>95.75868932452963</v>
+        <v>21.4992929753009</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>60.16640805476577</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.486602366484065</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.22427662294574</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.550777070673557</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
